--- a/Bancos_Sufijos_Pago_Prov_merge.xlsx
+++ b/Bancos_Sufijos_Pago_Prov_merge.xlsx
@@ -69,7 +69,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -78,6 +78,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -576,14 +577,20 @@
           <t>BANKIA, S.A.</t>
         </is>
       </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
+      <c r="M2" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N2" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O2" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -647,14 +654,20 @@
           <t>BANCO BILBAO VIZCAYA ARGENTARIA, S.A.</t>
         </is>
       </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -718,14 +731,20 @@
           <t>BANCO BILBAO VIZCAYA ARGENTARIA, S.A.</t>
         </is>
       </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O4" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -789,14 +808,20 @@
           <t>BANCO BILBAO VIZCAYA ARGENTARIA, S.A.</t>
         </is>
       </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -860,14 +885,20 @@
           <t>BANCO BILBAO VIZCAYA ARGENTARIA, S.A.</t>
         </is>
       </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O6" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -931,14 +962,20 @@
           <t>BANCO BILBAO VIZCAYA ARGENTARIA, S.A.</t>
         </is>
       </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O7" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -1002,14 +1039,20 @@
           <t>BANCO BILBAO VIZCAYA ARGENTARIA, S.A.</t>
         </is>
       </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O8" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -1073,14 +1116,20 @@
           <t>BANCO BILBAO VIZCAYA ARGENTARIA, S.A.</t>
         </is>
       </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O9" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -1144,14 +1193,20 @@
           <t>BANCO BILBAO VIZCAYA ARGENTARIA, S.A.</t>
         </is>
       </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N10" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O10" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1215,14 +1270,20 @@
           <t>BANCO BILBAO VIZCAYA ARGENTARIA, S.A.</t>
         </is>
       </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O11" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -1286,14 +1347,20 @@
           <t>BANCO BILBAO VIZCAYA ARGENTARIA, S.A.</t>
         </is>
       </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N12" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O12" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -1357,14 +1424,20 @@
           <t>BANCO BILBAO VIZCAYA ARGENTARIA, S.A.</t>
         </is>
       </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
+      <c r="M13" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O13" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -1428,14 +1501,20 @@
           <t>BANCO BILBAO VIZCAYA ARGENTARIA, S.A.</t>
         </is>
       </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
+      <c r="M14" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N14" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O14" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1499,14 +1578,20 @@
           <t>BANCO BILBAO VIZCAYA ARGENTARIA, S.A.</t>
         </is>
       </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
+      <c r="M15" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N15" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O15" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -1570,14 +1655,20 @@
           <t>BANCO BILBAO VIZCAYA ARGENTARIA, S.A.</t>
         </is>
       </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
+      <c r="M16" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N16" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O16" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -1641,14 +1732,20 @@
           <t>BANCO BILBAO VIZCAYA ARGENTARIA, S.A.</t>
         </is>
       </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
+      <c r="M17" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O17" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -1712,14 +1809,20 @@
           <t>BANCO BILBAO VIZCAYA ARGENTARIA, S.A.</t>
         </is>
       </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
+      <c r="M18" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N18" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O18" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1783,14 +1886,20 @@
           <t>BANCO BILBAO VIZCAYA ARGENTARIA, S.A.</t>
         </is>
       </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
+      <c r="M19" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N19" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O19" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -1846,14 +1955,20 @@
           <t>Credit Suisse CCC-5200 0006 3178 EUROS</t>
         </is>
       </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
+      <c r="M20" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N20" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O20" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -1909,14 +2024,20 @@
           <t>ABANCA CORPORACION BANCARIA, S.A.</t>
         </is>
       </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
+      <c r="M21" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N21" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O21" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -1980,15 +2101,17 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="inlineStr">
+      <c r="M22" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N22" s="4" t="inlineStr">
         <is>
           <t>023</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="O22" s="4" t="inlineStr">
         <is>
           <t>023</t>
         </is>
@@ -2055,15 +2178,17 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="inlineStr">
+      <c r="M23" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N23" s="4" t="inlineStr">
         <is>
           <t>023</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="O23" s="4" t="inlineStr">
         <is>
           <t>023</t>
         </is>
@@ -2130,14 +2255,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
+      <c r="M24" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N24" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O24" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -2201,14 +2332,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
+      <c r="M25" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N25" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O25" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -2272,14 +2409,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M26" t="n">
-        <v>666</v>
-      </c>
-      <c r="N26" t="n">
-        <v>666</v>
-      </c>
-      <c r="O26" t="n">
-        <v>606</v>
+      <c r="M26" s="4" t="inlineStr">
+        <is>
+          <t>666</t>
+        </is>
+      </c>
+      <c r="N26" s="4" t="inlineStr">
+        <is>
+          <t>666</t>
+        </is>
+      </c>
+      <c r="O26" s="4" t="inlineStr">
+        <is>
+          <t>606</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -2343,14 +2486,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M27" t="n">
-        <v>666</v>
-      </c>
-      <c r="N27" t="n">
-        <v>666</v>
-      </c>
-      <c r="O27" t="n">
-        <v>606</v>
+      <c r="M27" s="4" t="inlineStr">
+        <is>
+          <t>666</t>
+        </is>
+      </c>
+      <c r="N27" s="4" t="inlineStr">
+        <is>
+          <t>666</t>
+        </is>
+      </c>
+      <c r="O27" s="4" t="inlineStr">
+        <is>
+          <t>606</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -2414,17 +2563,17 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="M28" s="4" t="inlineStr">
         <is>
           <t>002</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="N28" s="4" t="inlineStr">
         <is>
           <t>002</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="O28" s="4" t="inlineStr">
         <is>
           <t>002</t>
         </is>
@@ -2491,17 +2640,17 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="M29" s="4" t="inlineStr">
         <is>
           <t>002</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="N29" s="4" t="inlineStr">
         <is>
           <t>002</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="O29" s="4" t="inlineStr">
         <is>
           <t>002</t>
         </is>
@@ -2568,14 +2717,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M30" t="n">
-        <v>111</v>
-      </c>
-      <c r="N30" t="n">
-        <v>111</v>
-      </c>
-      <c r="O30" t="n">
-        <v>101</v>
+      <c r="M30" s="4" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="N30" s="4" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="O30" s="4" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -2639,14 +2794,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M31" t="n">
-        <v>111</v>
-      </c>
-      <c r="N31" t="n">
-        <v>111</v>
-      </c>
-      <c r="O31" t="n">
-        <v>101</v>
+      <c r="M31" s="4" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="N31" s="4" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="O31" s="4" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -2710,14 +2871,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
+      <c r="M32" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N32" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O32" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="33">
@@ -2781,14 +2948,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
+      <c r="M33" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N33" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O33" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -2852,14 +3025,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
+      <c r="M34" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N34" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O34" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="35">
@@ -2923,14 +3102,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
+      <c r="M35" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N35" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O35" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="36">
@@ -2994,14 +3179,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
+      <c r="M36" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N36" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O36" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="37">
@@ -3065,14 +3256,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M37" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" t="n">
-        <v>822</v>
-      </c>
-      <c r="O37" t="n">
-        <v>822</v>
+      <c r="M37" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N37" s="4" t="inlineStr">
+        <is>
+          <t>822</t>
+        </is>
+      </c>
+      <c r="O37" s="4" t="inlineStr">
+        <is>
+          <t>822</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -3136,14 +3333,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M38" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" t="n">
-        <v>822</v>
-      </c>
-      <c r="O38" t="n">
-        <v>822</v>
+      <c r="M38" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N38" s="4" t="inlineStr">
+        <is>
+          <t>822</t>
+        </is>
+      </c>
+      <c r="O38" s="4" t="inlineStr">
+        <is>
+          <t>822</t>
+        </is>
       </c>
     </row>
     <row r="39">
@@ -3207,14 +3410,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M39" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" t="n">
-        <v>350</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
+      <c r="M39" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N39" s="4" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="O39" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -3278,14 +3487,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M40" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" t="n">
-        <v>350</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0</v>
+      <c r="M40" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N40" s="4" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="O40" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="41">
@@ -3349,14 +3564,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M41" t="n">
-        <v>181</v>
-      </c>
-      <c r="N41" t="n">
-        <v>181</v>
-      </c>
-      <c r="O41" t="n">
-        <v>181</v>
+      <c r="M41" s="4" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="N41" s="4" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="O41" s="4" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
       </c>
     </row>
     <row r="42">
@@ -3420,14 +3641,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M42" t="n">
-        <v>181</v>
-      </c>
-      <c r="N42" t="n">
-        <v>181</v>
-      </c>
-      <c r="O42" t="n">
-        <v>181</v>
+      <c r="M42" s="4" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="N42" s="4" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="O42" s="4" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
       </c>
     </row>
     <row r="43">
@@ -3491,14 +3718,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M43" t="n">
-        <v>777</v>
-      </c>
-      <c r="N43" t="n">
-        <v>777</v>
-      </c>
-      <c r="O43" t="n">
-        <v>707</v>
+      <c r="M43" s="4" t="inlineStr">
+        <is>
+          <t>777</t>
+        </is>
+      </c>
+      <c r="N43" s="4" t="inlineStr">
+        <is>
+          <t>777</t>
+        </is>
+      </c>
+      <c r="O43" s="4" t="inlineStr">
+        <is>
+          <t>707</t>
+        </is>
       </c>
     </row>
     <row r="44">
@@ -3562,14 +3795,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M44" t="n">
-        <v>777</v>
-      </c>
-      <c r="N44" t="n">
-        <v>777</v>
-      </c>
-      <c r="O44" t="n">
-        <v>707</v>
+      <c r="M44" s="4" t="inlineStr">
+        <is>
+          <t>777</t>
+        </is>
+      </c>
+      <c r="N44" s="4" t="inlineStr">
+        <is>
+          <t>777</t>
+        </is>
+      </c>
+      <c r="O44" s="4" t="inlineStr">
+        <is>
+          <t>707</t>
+        </is>
       </c>
     </row>
     <row r="45">
@@ -3633,17 +3872,17 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="M45" s="4" t="inlineStr">
         <is>
           <t>007</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="N45" s="4" t="inlineStr">
         <is>
           <t>007</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
+      <c r="O45" s="4" t="inlineStr">
         <is>
           <t>007</t>
         </is>
@@ -3710,17 +3949,17 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="M46" s="4" t="inlineStr">
         <is>
           <t>007</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="N46" s="4" t="inlineStr">
         <is>
           <t>007</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr">
+      <c r="O46" s="4" t="inlineStr">
         <is>
           <t>007</t>
         </is>
@@ -3787,16 +4026,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M47" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" t="inlineStr">
+      <c r="M47" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N47" s="4" t="inlineStr">
         <is>
           <t>025</t>
         </is>
       </c>
-      <c r="O47" t="n">
-        <v>0</v>
+      <c r="O47" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="48">
@@ -3860,16 +4103,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M48" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" t="inlineStr">
+      <c r="M48" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N48" s="4" t="inlineStr">
         <is>
           <t>025</t>
         </is>
       </c>
-      <c r="O48" t="n">
-        <v>0</v>
+      <c r="O48" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="49">
@@ -3933,14 +4180,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M49" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" t="n">
-        <v>100</v>
-      </c>
-      <c r="O49" t="n">
-        <v>0</v>
+      <c r="M49" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N49" s="4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="O49" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="50">
@@ -4004,14 +4257,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" t="n">
-        <v>100</v>
-      </c>
-      <c r="O50" t="n">
-        <v>0</v>
+      <c r="M50" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N50" s="4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="O50" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="51">
@@ -4075,17 +4334,17 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="M51" s="4" t="inlineStr">
         <is>
           <t>005</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="N51" s="4" t="inlineStr">
         <is>
           <t>005</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
+      <c r="O51" s="4" t="inlineStr">
         <is>
           <t>005</t>
         </is>
@@ -4152,17 +4411,17 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="M52" s="4" t="inlineStr">
         <is>
           <t>005</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
+      <c r="N52" s="4" t="inlineStr">
         <is>
           <t>005</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr">
+      <c r="O52" s="4" t="inlineStr">
         <is>
           <t>005</t>
         </is>
@@ -4229,14 +4488,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M53" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" t="n">
-        <v>240</v>
-      </c>
-      <c r="O53" t="n">
-        <v>0</v>
+      <c r="M53" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N53" s="4" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="O53" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="54">
@@ -4300,14 +4565,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M54" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" t="n">
-        <v>240</v>
-      </c>
-      <c r="O54" t="n">
-        <v>0</v>
+      <c r="M54" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N54" s="4" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="O54" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="55">
@@ -4371,14 +4642,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M55" t="n">
-        <v>999</v>
-      </c>
-      <c r="N55" t="n">
-        <v>999</v>
-      </c>
-      <c r="O55" t="n">
-        <v>909</v>
+      <c r="M55" s="4" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="N55" s="4" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="O55" s="4" t="inlineStr">
+        <is>
+          <t>909</t>
+        </is>
       </c>
     </row>
     <row r="56">
@@ -4442,14 +4719,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M56" t="n">
-        <v>999</v>
-      </c>
-      <c r="N56" t="n">
-        <v>999</v>
-      </c>
-      <c r="O56" t="n">
-        <v>909</v>
+      <c r="M56" s="4" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="N56" s="4" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="O56" s="4" t="inlineStr">
+        <is>
+          <t>909</t>
+        </is>
       </c>
     </row>
     <row r="57">
@@ -4513,14 +4796,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M57" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" t="n">
-        <v>0</v>
-      </c>
-      <c r="O57" t="n">
-        <v>0</v>
+      <c r="M57" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N57" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O57" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="58">
@@ -4584,14 +4873,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M58" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" t="n">
-        <v>0</v>
+      <c r="M58" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N58" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O58" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="59">
@@ -4655,14 +4950,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M59" t="n">
-        <v>0</v>
-      </c>
-      <c r="N59" t="n">
-        <v>899</v>
-      </c>
-      <c r="O59" t="n">
-        <v>0</v>
+      <c r="M59" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N59" s="4" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="O59" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="60">
@@ -4726,14 +5027,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M60" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" t="n">
-        <v>899</v>
-      </c>
-      <c r="O60" t="n">
-        <v>0</v>
+      <c r="M60" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N60" s="4" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="O60" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="61">
@@ -4797,14 +5104,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M61" t="n">
-        <v>555</v>
-      </c>
-      <c r="N61" t="n">
-        <v>555</v>
-      </c>
-      <c r="O61" t="n">
-        <v>505</v>
+      <c r="M61" s="4" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="N61" s="4" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="O61" s="4" t="inlineStr">
+        <is>
+          <t>505</t>
+        </is>
       </c>
     </row>
     <row r="62">
@@ -4868,14 +5181,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M62" t="n">
-        <v>555</v>
-      </c>
-      <c r="N62" t="n">
-        <v>555</v>
-      </c>
-      <c r="O62" t="n">
-        <v>505</v>
+      <c r="M62" s="4" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="N62" s="4" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="O62" s="4" t="inlineStr">
+        <is>
+          <t>505</t>
+        </is>
       </c>
     </row>
     <row r="63">
@@ -4939,16 +5258,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M63" t="n">
-        <v>0</v>
-      </c>
-      <c r="N63" t="inlineStr">
+      <c r="M63" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N63" s="4" t="inlineStr">
         <is>
           <t>010</t>
         </is>
       </c>
-      <c r="O63" t="n">
-        <v>0</v>
+      <c r="O63" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="64">
@@ -5012,16 +5335,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M64" t="n">
-        <v>0</v>
-      </c>
-      <c r="N64" t="inlineStr">
+      <c r="M64" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N64" s="4" t="inlineStr">
         <is>
           <t>010</t>
         </is>
       </c>
-      <c r="O64" t="n">
-        <v>0</v>
+      <c r="O64" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="65">
@@ -5085,14 +5412,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M65" t="n">
-        <v>0</v>
-      </c>
-      <c r="N65" t="n">
-        <v>663</v>
-      </c>
-      <c r="O65" t="n">
-        <v>663</v>
+      <c r="M65" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N65" s="4" t="inlineStr">
+        <is>
+          <t>663</t>
+        </is>
+      </c>
+      <c r="O65" s="4" t="inlineStr">
+        <is>
+          <t>663</t>
+        </is>
       </c>
     </row>
     <row r="66">
@@ -5156,14 +5489,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N66" t="n">
-        <v>663</v>
-      </c>
-      <c r="O66" t="n">
-        <v>663</v>
+      <c r="M66" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N66" s="4" t="inlineStr">
+        <is>
+          <t>663</t>
+        </is>
+      </c>
+      <c r="O66" s="4" t="inlineStr">
+        <is>
+          <t>663</t>
+        </is>
       </c>
     </row>
     <row r="67">
@@ -5227,17 +5566,17 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr">
+      <c r="M67" s="4" t="inlineStr">
         <is>
           <t>001</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr">
+      <c r="N67" s="4" t="inlineStr">
         <is>
           <t>001</t>
         </is>
       </c>
-      <c r="O67" t="inlineStr">
+      <c r="O67" s="4" t="inlineStr">
         <is>
           <t>001</t>
         </is>
@@ -5304,17 +5643,17 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr">
+      <c r="M68" s="4" t="inlineStr">
         <is>
           <t>001</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr">
+      <c r="N68" s="4" t="inlineStr">
         <is>
           <t>001</t>
         </is>
       </c>
-      <c r="O68" t="inlineStr">
+      <c r="O68" s="4" t="inlineStr">
         <is>
           <t>001</t>
         </is>
@@ -5381,14 +5720,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M69" t="n">
-        <v>0</v>
-      </c>
-      <c r="N69" t="n">
-        <v>0</v>
-      </c>
-      <c r="O69" t="n">
-        <v>0</v>
+      <c r="M69" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N69" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O69" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="70">
@@ -5452,14 +5797,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M70" t="n">
-        <v>0</v>
-      </c>
-      <c r="N70" t="n">
-        <v>0</v>
-      </c>
-      <c r="O70" t="n">
-        <v>0</v>
+      <c r="M70" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N70" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O70" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="71">
@@ -5523,14 +5874,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M71" t="n">
-        <v>0</v>
-      </c>
-      <c r="N71" t="n">
-        <v>0</v>
-      </c>
-      <c r="O71" t="n">
-        <v>0</v>
+      <c r="M71" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N71" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O71" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="72">
@@ -5594,14 +5951,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M72" t="n">
-        <v>0</v>
-      </c>
-      <c r="N72" t="n">
-        <v>0</v>
-      </c>
-      <c r="O72" t="n">
-        <v>0</v>
+      <c r="M72" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N72" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O72" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="73">
@@ -5665,14 +6028,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M73" t="n">
-        <v>0</v>
-      </c>
-      <c r="N73" t="n">
-        <v>0</v>
-      </c>
-      <c r="O73" t="n">
-        <v>0</v>
+      <c r="M73" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N73" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O73" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="74">
@@ -5736,14 +6105,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M74" t="n">
-        <v>0</v>
-      </c>
-      <c r="N74" t="n">
-        <v>0</v>
-      </c>
-      <c r="O74" t="n">
-        <v>0</v>
+      <c r="M74" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N74" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O74" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="75">
@@ -5807,14 +6182,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M75" t="n">
-        <v>0</v>
-      </c>
-      <c r="N75" t="n">
-        <v>0</v>
-      </c>
-      <c r="O75" t="n">
-        <v>0</v>
+      <c r="M75" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N75" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O75" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="76">
@@ -5878,14 +6259,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M76" t="n">
-        <v>0</v>
-      </c>
-      <c r="N76" t="n">
-        <v>0</v>
-      </c>
-      <c r="O76" t="n">
-        <v>0</v>
+      <c r="M76" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N76" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O76" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="77">
@@ -5949,14 +6336,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M77" t="n">
-        <v>0</v>
-      </c>
-      <c r="N77" t="n">
-        <v>0</v>
-      </c>
-      <c r="O77" t="n">
-        <v>0</v>
+      <c r="M77" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N77" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O77" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="78">
@@ -6020,14 +6413,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M78" t="n">
-        <v>0</v>
-      </c>
-      <c r="N78" t="n">
-        <v>0</v>
-      </c>
-      <c r="O78" t="n">
-        <v>0</v>
+      <c r="M78" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N78" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O78" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="79">
@@ -6091,14 +6490,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M79" t="n">
-        <v>0</v>
-      </c>
-      <c r="N79" t="n">
-        <v>0</v>
-      </c>
-      <c r="O79" t="n">
-        <v>0</v>
+      <c r="M79" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N79" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O79" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="80">
@@ -6162,18 +6567,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M80" t="inlineStr">
+      <c r="M80" s="4" t="inlineStr">
         <is>
           <t>006</t>
         </is>
       </c>
-      <c r="N80" t="inlineStr">
+      <c r="N80" s="4" t="inlineStr">
         <is>
           <t>006</t>
         </is>
       </c>
-      <c r="O80" t="n">
-        <v>0</v>
+      <c r="O80" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="81">
@@ -6237,18 +6644,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M81" t="inlineStr">
+      <c r="M81" s="4" t="inlineStr">
         <is>
           <t>006</t>
         </is>
       </c>
-      <c r="N81" t="inlineStr">
+      <c r="N81" s="4" t="inlineStr">
         <is>
           <t>006</t>
         </is>
       </c>
-      <c r="O81" t="n">
-        <v>0</v>
+      <c r="O81" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="82">
@@ -6312,14 +6721,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M82" t="n">
-        <v>0</v>
-      </c>
-      <c r="N82" t="n">
-        <v>888</v>
-      </c>
-      <c r="O82" t="n">
-        <v>0</v>
+      <c r="M82" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N82" s="4" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="O82" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="83">
@@ -6383,14 +6798,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M83" t="n">
-        <v>0</v>
-      </c>
-      <c r="N83" t="n">
-        <v>888</v>
-      </c>
-      <c r="O83" t="n">
-        <v>0</v>
+      <c r="M83" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N83" s="4" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="O83" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="84">
@@ -6454,14 +6875,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M84" t="n">
-        <v>0</v>
-      </c>
-      <c r="N84" t="n">
-        <v>153</v>
-      </c>
-      <c r="O84" t="n">
-        <v>0</v>
+      <c r="M84" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N84" s="4" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="O84" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="85">
@@ -6525,14 +6952,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M85" t="n">
-        <v>0</v>
-      </c>
-      <c r="N85" t="n">
-        <v>153</v>
-      </c>
-      <c r="O85" t="n">
-        <v>0</v>
+      <c r="M85" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N85" s="4" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="O85" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="86">
@@ -6596,14 +7029,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M86" t="n">
-        <v>333</v>
-      </c>
-      <c r="N86" t="n">
-        <v>333</v>
-      </c>
-      <c r="O86" t="n">
-        <v>303</v>
+      <c r="M86" s="4" t="inlineStr">
+        <is>
+          <t>333</t>
+        </is>
+      </c>
+      <c r="N86" s="4" t="inlineStr">
+        <is>
+          <t>333</t>
+        </is>
+      </c>
+      <c r="O86" s="4" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
       </c>
     </row>
     <row r="87">
@@ -6667,14 +7106,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M87" t="n">
-        <v>333</v>
-      </c>
-      <c r="N87" t="n">
-        <v>333</v>
-      </c>
-      <c r="O87" t="n">
-        <v>303</v>
+      <c r="M87" s="4" t="inlineStr">
+        <is>
+          <t>333</t>
+        </is>
+      </c>
+      <c r="N87" s="4" t="inlineStr">
+        <is>
+          <t>333</t>
+        </is>
+      </c>
+      <c r="O87" s="4" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
       </c>
     </row>
     <row r="88">
@@ -6738,14 +7183,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M88" t="n">
-        <v>0</v>
-      </c>
-      <c r="N88" t="n">
-        <v>360</v>
-      </c>
-      <c r="O88" t="n">
-        <v>0</v>
+      <c r="M88" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N88" s="4" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="O88" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="89">
@@ -6809,14 +7260,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M89" t="n">
-        <v>0</v>
-      </c>
-      <c r="N89" t="n">
-        <v>360</v>
-      </c>
-      <c r="O89" t="n">
-        <v>0</v>
+      <c r="M89" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N89" s="4" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="O89" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="90">
@@ -6880,14 +7337,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M90" t="n">
-        <v>222</v>
-      </c>
-      <c r="N90" t="n">
-        <v>222</v>
-      </c>
-      <c r="O90" t="n">
-        <v>222</v>
+      <c r="M90" s="4" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="N90" s="4" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="O90" s="4" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
       </c>
     </row>
     <row r="91">
@@ -6951,14 +7414,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M91" t="n">
-        <v>222</v>
-      </c>
-      <c r="N91" t="n">
-        <v>222</v>
-      </c>
-      <c r="O91" t="n">
-        <v>222</v>
+      <c r="M91" s="4" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="N91" s="4" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="O91" s="4" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
       </c>
     </row>
     <row r="92">
@@ -7022,14 +7491,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M92" t="n">
-        <v>0</v>
-      </c>
-      <c r="N92" t="n">
-        <v>101</v>
-      </c>
-      <c r="O92" t="n">
-        <v>0</v>
+      <c r="M92" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N92" s="4" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="O92" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="93">
@@ -7093,14 +7568,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M93" t="n">
-        <v>0</v>
-      </c>
-      <c r="N93" t="n">
-        <v>101</v>
-      </c>
-      <c r="O93" t="n">
-        <v>0</v>
+      <c r="M93" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N93" s="4" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="O93" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="94">
@@ -7164,14 +7645,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M94" t="n">
-        <v>444</v>
-      </c>
-      <c r="N94" t="n">
-        <v>444</v>
-      </c>
-      <c r="O94" t="n">
-        <v>404</v>
+      <c r="M94" s="4" t="inlineStr">
+        <is>
+          <t>444</t>
+        </is>
+      </c>
+      <c r="N94" s="4" t="inlineStr">
+        <is>
+          <t>444</t>
+        </is>
+      </c>
+      <c r="O94" s="4" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
       </c>
     </row>
     <row r="95">
@@ -7235,14 +7722,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M95" t="n">
-        <v>444</v>
-      </c>
-      <c r="N95" t="n">
-        <v>444</v>
-      </c>
-      <c r="O95" t="n">
-        <v>404</v>
+      <c r="M95" s="4" t="inlineStr">
+        <is>
+          <t>444</t>
+        </is>
+      </c>
+      <c r="N95" s="4" t="inlineStr">
+        <is>
+          <t>444</t>
+        </is>
+      </c>
+      <c r="O95" s="4" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
       </c>
     </row>
     <row r="96">
@@ -7306,14 +7799,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M96" t="n">
-        <v>0</v>
-      </c>
-      <c r="N96" t="n">
-        <v>0</v>
-      </c>
-      <c r="O96" t="n">
-        <v>0</v>
+      <c r="M96" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N96" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O96" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="97">
@@ -7377,14 +7876,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M97" t="n">
-        <v>0</v>
-      </c>
-      <c r="N97" t="n">
-        <v>0</v>
-      </c>
-      <c r="O97" t="n">
-        <v>0</v>
+      <c r="M97" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N97" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O97" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="98">
@@ -7448,14 +7953,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M98" t="n">
-        <v>0</v>
-      </c>
-      <c r="N98" t="n">
-        <v>0</v>
-      </c>
-      <c r="O98" t="n">
-        <v>0</v>
+      <c r="M98" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N98" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O98" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="99">
@@ -7519,14 +8030,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M99" t="n">
-        <v>0</v>
-      </c>
-      <c r="N99" t="n">
-        <v>0</v>
-      </c>
-      <c r="O99" t="n">
-        <v>0</v>
+      <c r="M99" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N99" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O99" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="100">
@@ -7590,14 +8107,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M100" t="n">
-        <v>0</v>
-      </c>
-      <c r="N100" t="n">
-        <v>0</v>
-      </c>
-      <c r="O100" t="n">
-        <v>0</v>
+      <c r="M100" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N100" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O100" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="101">
@@ -7661,14 +8184,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M101" t="n">
-        <v>0</v>
-      </c>
-      <c r="N101" t="n">
-        <v>0</v>
-      </c>
-      <c r="O101" t="n">
-        <v>0</v>
+      <c r="M101" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N101" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O101" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="102">
@@ -7732,14 +8261,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M102" t="n">
-        <v>0</v>
-      </c>
-      <c r="N102" t="n">
-        <v>0</v>
-      </c>
-      <c r="O102" t="n">
-        <v>0</v>
+      <c r="M102" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N102" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O102" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="103">
@@ -7803,14 +8338,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M103" t="n">
-        <v>0</v>
-      </c>
-      <c r="N103" t="n">
-        <v>0</v>
-      </c>
-      <c r="O103" t="n">
-        <v>0</v>
+      <c r="M103" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N103" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O103" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="104">
@@ -7874,14 +8415,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M104" t="n">
-        <v>0</v>
-      </c>
-      <c r="N104" t="n">
-        <v>0</v>
-      </c>
-      <c r="O104" t="n">
-        <v>0</v>
+      <c r="M104" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N104" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O104" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="105">
@@ -7945,14 +8492,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M105" t="n">
-        <v>0</v>
-      </c>
-      <c r="N105" t="n">
-        <v>0</v>
-      </c>
-      <c r="O105" t="n">
-        <v>0</v>
+      <c r="M105" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N105" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O105" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="106">
@@ -8016,14 +8569,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M106" t="n">
-        <v>0</v>
-      </c>
-      <c r="N106" t="n">
-        <v>0</v>
-      </c>
-      <c r="O106" t="n">
-        <v>0</v>
+      <c r="M106" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N106" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O106" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="107">
@@ -8087,16 +8646,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M107" t="n">
-        <v>0</v>
-      </c>
-      <c r="N107" t="inlineStr">
+      <c r="M107" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N107" s="4" t="inlineStr">
         <is>
           <t>004</t>
         </is>
       </c>
-      <c r="O107" t="n">
-        <v>0</v>
+      <c r="O107" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="108">
@@ -8160,16 +8723,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M108" t="n">
-        <v>0</v>
-      </c>
-      <c r="N108" t="inlineStr">
+      <c r="M108" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N108" s="4" t="inlineStr">
         <is>
           <t>004</t>
         </is>
       </c>
-      <c r="O108" t="n">
-        <v>0</v>
+      <c r="O108" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="109">
@@ -8233,14 +8800,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M109" t="n">
-        <v>0</v>
-      </c>
-      <c r="N109" t="n">
-        <v>617</v>
-      </c>
-      <c r="O109" t="n">
-        <v>0</v>
+      <c r="M109" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N109" s="4" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="O109" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="110">
@@ -8304,14 +8877,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M110" t="n">
-        <v>0</v>
-      </c>
-      <c r="N110" t="n">
-        <v>617</v>
-      </c>
-      <c r="O110" t="n">
-        <v>0</v>
+      <c r="M110" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N110" s="4" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="O110" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="111">
@@ -8375,15 +8954,17 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M111" t="n">
-        <v>0</v>
-      </c>
-      <c r="N111" t="inlineStr">
+      <c r="M111" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N111" s="4" t="inlineStr">
         <is>
           <t>021</t>
         </is>
       </c>
-      <c r="O111" t="inlineStr">
+      <c r="O111" s="4" t="inlineStr">
         <is>
           <t>021</t>
         </is>
@@ -8450,15 +9031,17 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M112" t="n">
-        <v>0</v>
-      </c>
-      <c r="N112" t="inlineStr">
+      <c r="M112" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N112" s="4" t="inlineStr">
         <is>
           <t>021</t>
         </is>
       </c>
-      <c r="O112" t="inlineStr">
+      <c r="O112" s="4" t="inlineStr">
         <is>
           <t>021</t>
         </is>
@@ -8525,15 +9108,17 @@
           <t>Bankinter CC/0100009234. aaSA COBROS</t>
         </is>
       </c>
-      <c r="M113" t="n">
-        <v>0</v>
-      </c>
-      <c r="N113" t="inlineStr">
+      <c r="M113" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N113" s="4" t="inlineStr">
         <is>
           <t>021</t>
         </is>
       </c>
-      <c r="O113" t="inlineStr">
+      <c r="O113" s="4" t="inlineStr">
         <is>
           <t>021</t>
         </is>
@@ -8600,15 +9185,17 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M114" t="n">
-        <v>0</v>
-      </c>
-      <c r="N114" t="inlineStr">
+      <c r="M114" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N114" s="4" t="inlineStr">
         <is>
           <t>021</t>
         </is>
       </c>
-      <c r="O114" t="inlineStr">
+      <c r="O114" s="4" t="inlineStr">
         <is>
           <t>021</t>
         </is>
@@ -8675,15 +9262,17 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M115" t="n">
-        <v>0</v>
-      </c>
-      <c r="N115" t="inlineStr">
+      <c r="M115" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N115" s="4" t="inlineStr">
         <is>
           <t>021</t>
         </is>
       </c>
-      <c r="O115" t="inlineStr">
+      <c r="O115" s="4" t="inlineStr">
         <is>
           <t>021</t>
         </is>
@@ -8750,17 +9339,17 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M116" t="inlineStr">
+      <c r="M116" s="4" t="inlineStr">
         <is>
           <t>008</t>
         </is>
       </c>
-      <c r="N116" t="inlineStr">
+      <c r="N116" s="4" t="inlineStr">
         <is>
           <t>008</t>
         </is>
       </c>
-      <c r="O116" t="inlineStr">
+      <c r="O116" s="4" t="inlineStr">
         <is>
           <t>008</t>
         </is>
@@ -8827,17 +9416,17 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M117" t="inlineStr">
+      <c r="M117" s="4" t="inlineStr">
         <is>
           <t>008</t>
         </is>
       </c>
-      <c r="N117" t="inlineStr">
+      <c r="N117" s="4" t="inlineStr">
         <is>
           <t>008</t>
         </is>
       </c>
-      <c r="O117" t="inlineStr">
+      <c r="O117" s="4" t="inlineStr">
         <is>
           <t>008</t>
         </is>
@@ -8904,14 +9493,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M118" t="n">
-        <v>0</v>
-      </c>
-      <c r="N118" t="n">
-        <v>0</v>
-      </c>
-      <c r="O118" t="n">
-        <v>0</v>
+      <c r="M118" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N118" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O118" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="119">
@@ -8975,14 +9570,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M119" t="n">
-        <v>0</v>
-      </c>
-      <c r="N119" t="n">
-        <v>0</v>
-      </c>
-      <c r="O119" t="n">
-        <v>0</v>
+      <c r="M119" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N119" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O119" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="120">
@@ -9046,14 +9647,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M120" t="n">
-        <v>0</v>
-      </c>
-      <c r="N120" t="n">
-        <v>0</v>
-      </c>
-      <c r="O120" t="n">
-        <v>0</v>
+      <c r="M120" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N120" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O120" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="121">
@@ -9117,14 +9724,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M121" t="n">
-        <v>0</v>
-      </c>
-      <c r="N121" t="n">
-        <v>0</v>
-      </c>
-      <c r="O121" t="n">
-        <v>0</v>
+      <c r="M121" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N121" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O121" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="122">
@@ -9188,15 +9801,17 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M122" t="n">
-        <v>0</v>
-      </c>
-      <c r="N122" t="inlineStr">
+      <c r="M122" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N122" s="4" t="inlineStr">
         <is>
           <t>020</t>
         </is>
       </c>
-      <c r="O122" t="inlineStr">
+      <c r="O122" s="4" t="inlineStr">
         <is>
           <t>020</t>
         </is>
@@ -9263,15 +9878,17 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M123" t="n">
-        <v>0</v>
-      </c>
-      <c r="N123" t="inlineStr">
+      <c r="M123" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N123" s="4" t="inlineStr">
         <is>
           <t>020</t>
         </is>
       </c>
-      <c r="O123" t="inlineStr">
+      <c r="O123" s="4" t="inlineStr">
         <is>
           <t>020</t>
         </is>
@@ -9338,14 +9955,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M124" t="n">
-        <v>0</v>
-      </c>
-      <c r="N124" t="n">
-        <v>180</v>
-      </c>
-      <c r="O124" t="n">
-        <v>0</v>
+      <c r="M124" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N124" s="4" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="O124" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="125">
@@ -9409,14 +10032,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M125" t="n">
-        <v>0</v>
-      </c>
-      <c r="N125" t="n">
-        <v>180</v>
-      </c>
-      <c r="O125" t="n">
-        <v>0</v>
+      <c r="M125" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N125" s="4" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="O125" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="126">
@@ -9480,16 +10109,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M126" t="n">
-        <v>0</v>
-      </c>
-      <c r="N126" t="inlineStr">
+      <c r="M126" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N126" s="4" t="inlineStr">
         <is>
           <t>003</t>
         </is>
       </c>
-      <c r="O126" t="n">
-        <v>0</v>
+      <c r="O126" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="127">
@@ -9553,16 +10186,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M127" t="n">
-        <v>0</v>
-      </c>
-      <c r="N127" t="inlineStr">
+      <c r="M127" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N127" s="4" t="inlineStr">
         <is>
           <t>003</t>
         </is>
       </c>
-      <c r="O127" t="n">
-        <v>0</v>
+      <c r="O127" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="128">
@@ -9626,14 +10263,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M128" t="n">
-        <v>222</v>
-      </c>
-      <c r="N128" t="n">
-        <v>222</v>
-      </c>
-      <c r="O128" t="n">
-        <v>202</v>
+      <c r="M128" s="4" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="N128" s="4" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="O128" s="4" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
       </c>
     </row>
     <row r="129">
@@ -9697,14 +10340,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M129" t="n">
-        <v>222</v>
-      </c>
-      <c r="N129" t="n">
-        <v>222</v>
-      </c>
-      <c r="O129" t="n">
-        <v>202</v>
+      <c r="M129" s="4" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="N129" s="4" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="O129" s="4" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
       </c>
     </row>
     <row r="130">
@@ -9768,14 +10417,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M130" t="n">
-        <v>0</v>
-      </c>
-      <c r="N130" t="n">
-        <v>200</v>
-      </c>
-      <c r="O130" t="n">
-        <v>0</v>
+      <c r="M130" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N130" s="4" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="O130" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="131">
@@ -9839,14 +10494,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M131" t="n">
-        <v>0</v>
-      </c>
-      <c r="N131" t="n">
-        <v>200</v>
-      </c>
-      <c r="O131" t="n">
-        <v>0</v>
+      <c r="M131" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N131" s="4" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="O131" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="132">
@@ -9910,17 +10571,17 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M132" t="inlineStr">
+      <c r="M132" s="4" t="inlineStr">
         <is>
           <t>002</t>
         </is>
       </c>
-      <c r="N132" t="inlineStr">
+      <c r="N132" s="4" t="inlineStr">
         <is>
           <t>002</t>
         </is>
       </c>
-      <c r="O132" t="inlineStr">
+      <c r="O132" s="4" t="inlineStr">
         <is>
           <t>002</t>
         </is>
@@ -9987,17 +10648,17 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M133" t="inlineStr">
+      <c r="M133" s="4" t="inlineStr">
         <is>
           <t>002</t>
         </is>
       </c>
-      <c r="N133" t="inlineStr">
+      <c r="N133" s="4" t="inlineStr">
         <is>
           <t>002</t>
         </is>
       </c>
-      <c r="O133" t="inlineStr">
+      <c r="O133" s="4" t="inlineStr">
         <is>
           <t>002</t>
         </is>
@@ -10064,14 +10725,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M134" t="n">
-        <v>0</v>
-      </c>
-      <c r="N134" t="n">
-        <v>282</v>
-      </c>
-      <c r="O134" t="n">
-        <v>0</v>
+      <c r="M134" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N134" s="4" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="O134" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="135">
@@ -10135,14 +10802,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M135" t="n">
-        <v>0</v>
-      </c>
-      <c r="N135" t="n">
-        <v>282</v>
-      </c>
-      <c r="O135" t="n">
-        <v>0</v>
+      <c r="M135" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N135" s="4" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="O135" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="136">
@@ -10198,14 +10871,20 @@
           <t>BANCA NAZIONALE DEL LAVORO</t>
         </is>
       </c>
-      <c r="M136" t="n">
-        <v>0</v>
-      </c>
-      <c r="N136" t="n">
-        <v>282</v>
-      </c>
-      <c r="O136" t="n">
-        <v>0</v>
+      <c r="M136" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N136" s="4" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="O136" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="137">
@@ -10261,14 +10940,20 @@
           <t>BNP PARIBAS S.A., S.E.</t>
         </is>
       </c>
-      <c r="M137" t="n">
-        <v>0</v>
-      </c>
-      <c r="N137" t="n">
-        <v>282</v>
-      </c>
-      <c r="O137" t="n">
-        <v>0</v>
+      <c r="M137" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N137" s="4" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="O137" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="138">
@@ -10324,14 +11009,20 @@
           <t>BNP PARIBAS S.A., S.E.</t>
         </is>
       </c>
-      <c r="M138" t="n">
-        <v>0</v>
-      </c>
-      <c r="N138" t="n">
-        <v>282</v>
-      </c>
-      <c r="O138" t="n">
-        <v>0</v>
+      <c r="M138" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N138" s="4" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="O138" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="139">
@@ -10387,14 +11078,20 @@
           <t>Banco Popular Aena AEROPUERTOS</t>
         </is>
       </c>
-      <c r="M139" t="n">
-        <v>0</v>
-      </c>
-      <c r="N139" t="n">
-        <v>282</v>
-      </c>
-      <c r="O139" t="n">
-        <v>0</v>
+      <c r="M139" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N139" s="4" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="O139" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="140">
@@ -10450,14 +11147,20 @@
           <t>Banco Sabadell Aena EPE</t>
         </is>
       </c>
-      <c r="M140" t="n">
-        <v>0</v>
-      </c>
-      <c r="N140" t="n">
-        <v>282</v>
-      </c>
-      <c r="O140" t="n">
-        <v>0</v>
+      <c r="M140" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N140" s="4" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="O140" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="141">
@@ -10513,14 +11216,20 @@
           <t>Banco Sabadell Aena AEROPUERTOS</t>
         </is>
       </c>
-      <c r="M141" t="n">
-        <v>0</v>
-      </c>
-      <c r="N141" t="n">
-        <v>282</v>
-      </c>
-      <c r="O141" t="n">
-        <v>0</v>
+      <c r="M141" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N141" s="4" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="O141" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="142">
@@ -10576,14 +11285,20 @@
           <t>BANCO DE SABADELL, S.A.</t>
         </is>
       </c>
-      <c r="M142" t="n">
-        <v>0</v>
-      </c>
-      <c r="N142" t="n">
-        <v>282</v>
-      </c>
-      <c r="O142" t="n">
-        <v>0</v>
+      <c r="M142" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N142" s="4" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="O142" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="143">
@@ -10639,14 +11354,20 @@
           <t>BANCO SANTANDER, S.A.</t>
         </is>
       </c>
-      <c r="M143" t="n">
-        <v>0</v>
-      </c>
-      <c r="N143" t="n">
-        <v>282</v>
-      </c>
-      <c r="O143" t="n">
-        <v>0</v>
+      <c r="M143" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N143" s="4" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="O143" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="144">
@@ -10702,14 +11423,20 @@
           <t>BANCO SANTANDER, S.A.</t>
         </is>
       </c>
-      <c r="M144" t="n">
-        <v>0</v>
-      </c>
-      <c r="N144" t="n">
-        <v>0</v>
-      </c>
-      <c r="O144" t="n">
-        <v>0</v>
+      <c r="M144" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N144" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O144" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="145">
@@ -10765,14 +11492,20 @@
           <t>BANCO SANTANDER, S.A.</t>
         </is>
       </c>
-      <c r="M145" t="n">
-        <v>0</v>
-      </c>
-      <c r="N145" t="n">
-        <v>0</v>
-      </c>
-      <c r="O145" t="n">
-        <v>0</v>
+      <c r="M145" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N145" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O145" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="146">
@@ -10828,14 +11561,20 @@
           <t>BANCO SANTANDER, S.A.</t>
         </is>
       </c>
-      <c r="M146" t="n">
-        <v>0</v>
-      </c>
-      <c r="N146" t="n">
-        <v>0</v>
-      </c>
-      <c r="O146" t="n">
-        <v>0</v>
+      <c r="M146" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N146" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O146" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="147">
@@ -10891,14 +11630,20 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M147" t="n">
-        <v>0</v>
-      </c>
-      <c r="N147" t="n">
-        <v>0</v>
-      </c>
-      <c r="O147" t="n">
-        <v>0</v>
+      <c r="M147" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N147" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O147" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="148">
@@ -10954,14 +11699,20 @@
           <t>BANCO BILBAO VIZCAYA ARGENTARIA</t>
         </is>
       </c>
-      <c r="M148" t="n">
-        <v>0</v>
-      </c>
-      <c r="N148" t="n">
-        <v>0</v>
-      </c>
-      <c r="O148" t="n">
-        <v>0</v>
+      <c r="M148" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N148" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O148" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="149">
@@ -11017,14 +11768,20 @@
           <t>BANCO BILBAO VIZCAYA ARGENTARIA</t>
         </is>
       </c>
-      <c r="M149" t="n">
-        <v>0</v>
-      </c>
-      <c r="N149" t="n">
-        <v>0</v>
-      </c>
-      <c r="O149" t="n">
-        <v>0</v>
+      <c r="M149" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N149" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O149" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="150">
@@ -11080,14 +11837,20 @@
           <t>BANCO BILBAO VIZCAYA ARGENTARIA</t>
         </is>
       </c>
-      <c r="M150" t="n">
-        <v>0</v>
-      </c>
-      <c r="N150" t="n">
-        <v>0</v>
-      </c>
-      <c r="O150" t="n">
-        <v>0</v>
+      <c r="M150" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N150" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O150" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="151">
@@ -11143,14 +11906,20 @@
           <t>BANCO BILBAO VIZCAYA ARGENTARIA</t>
         </is>
       </c>
-      <c r="M151" t="n">
-        <v>0</v>
-      </c>
-      <c r="N151" t="n">
-        <v>0</v>
-      </c>
-      <c r="O151" t="n">
-        <v>0</v>
+      <c r="M151" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N151" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O151" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="152">
@@ -11206,14 +11975,20 @@
           <t>BANCO BILBAO VIZCAYA ARGENTARIA</t>
         </is>
       </c>
-      <c r="M152" t="n">
-        <v>0</v>
-      </c>
-      <c r="N152" t="n">
-        <v>0</v>
-      </c>
-      <c r="O152" t="n">
-        <v>0</v>
+      <c r="M152" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N152" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O152" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="153">
@@ -11269,14 +12044,20 @@
           <t>BANCO BILBAO VIZCAYA ARGENTARIA</t>
         </is>
       </c>
-      <c r="M153" t="n">
-        <v>0</v>
-      </c>
-      <c r="N153" t="n">
-        <v>0</v>
-      </c>
-      <c r="O153" t="n">
-        <v>0</v>
+      <c r="M153" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N153" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O153" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="154">
@@ -11332,14 +12113,20 @@
           <t>BANCO BILBAO VIZCAYA ARGENTARIA</t>
         </is>
       </c>
-      <c r="M154" t="n">
-        <v>0</v>
-      </c>
-      <c r="N154" t="n">
-        <v>0</v>
-      </c>
-      <c r="O154" t="n">
-        <v>0</v>
+      <c r="M154" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N154" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O154" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="155">
@@ -11395,14 +12182,20 @@
           <t>BANCO BILBAO VIZCAYA ARGENTARIA</t>
         </is>
       </c>
-      <c r="M155" t="n">
-        <v>0</v>
-      </c>
-      <c r="N155" t="n">
-        <v>0</v>
-      </c>
-      <c r="O155" t="n">
-        <v>0</v>
+      <c r="M155" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N155" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O155" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="156">
@@ -11458,14 +12251,20 @@
           <t>BANCO BILBAO VIZCAYA ARGENTARIA</t>
         </is>
       </c>
-      <c r="M156" t="n">
-        <v>0</v>
-      </c>
-      <c r="N156" t="n">
-        <v>0</v>
-      </c>
-      <c r="O156" t="n">
-        <v>0</v>
+      <c r="M156" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N156" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O156" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="157">
@@ -11521,14 +12320,20 @@
           <t>BANCO BILBAO VIZCAYA ARGENTARIA</t>
         </is>
       </c>
-      <c r="M157" t="n">
-        <v>0</v>
-      </c>
-      <c r="N157" t="n">
-        <v>0</v>
-      </c>
-      <c r="O157" t="n">
-        <v>0</v>
+      <c r="M157" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N157" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O157" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="158">
@@ -11584,14 +12389,20 @@
           <t>BANCO BILBAO VIZCAYA ARGENTARIA</t>
         </is>
       </c>
-      <c r="M158" t="n">
-        <v>0</v>
-      </c>
-      <c r="N158" t="n">
-        <v>0</v>
-      </c>
-      <c r="O158" t="n">
-        <v>0</v>
+      <c r="M158" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N158" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O158" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="159">
@@ -11647,14 +12458,20 @@
           <t>CREDIT AGRICOLE CORPORATE AND INVESTMENT BANK,S.E.</t>
         </is>
       </c>
-      <c r="M159" t="n">
-        <v>0</v>
-      </c>
-      <c r="N159" t="n">
-        <v>0</v>
-      </c>
-      <c r="O159" t="n">
-        <v>0</v>
+      <c r="M159" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N159" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O159" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="160">
@@ -11710,14 +12527,20 @@
           <t>CAJAMAR CAJA RURAL, S.C.C.</t>
         </is>
       </c>
-      <c r="M160" t="n">
-        <v>0</v>
-      </c>
-      <c r="N160" t="n">
-        <v>0</v>
-      </c>
-      <c r="O160" t="n">
-        <v>0</v>
+      <c r="M160" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N160" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O160" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="161">
@@ -11773,14 +12596,20 @@
           <t>Credit Suisse CCC-5200 0006 3178 EUROS</t>
         </is>
       </c>
-      <c r="M161" t="n">
-        <v>0</v>
-      </c>
-      <c r="N161" t="n">
-        <v>0</v>
-      </c>
-      <c r="O161" t="n">
-        <v>0</v>
+      <c r="M161" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N161" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O161" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="162">
@@ -11844,15 +12673,17 @@
           <t>CAIXABANK, S.A.</t>
         </is>
       </c>
-      <c r="M162" t="n">
-        <v>0</v>
-      </c>
-      <c r="N162" t="inlineStr">
+      <c r="M162" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N162" s="4" t="inlineStr">
         <is>
           <t>023</t>
         </is>
       </c>
-      <c r="O162" t="inlineStr">
+      <c r="O162" s="4" t="inlineStr">
         <is>
           <t>023</t>
         </is>
@@ -11919,15 +12750,17 @@
           <t>CAIXABANK, S.A.</t>
         </is>
       </c>
-      <c r="M163" t="n">
-        <v>0</v>
-      </c>
-      <c r="N163" t="inlineStr">
+      <c r="M163" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N163" s="4" t="inlineStr">
         <is>
           <t>023</t>
         </is>
       </c>
-      <c r="O163" t="inlineStr">
+      <c r="O163" s="4" t="inlineStr">
         <is>
           <t>023</t>
         </is>
@@ -11994,14 +12827,20 @@
           <t>CAIXABANK, S.A.</t>
         </is>
       </c>
-      <c r="M164" t="n">
-        <v>666</v>
-      </c>
-      <c r="N164" t="n">
-        <v>666</v>
-      </c>
-      <c r="O164" t="n">
-        <v>606</v>
+      <c r="M164" s="4" t="inlineStr">
+        <is>
+          <t>666</t>
+        </is>
+      </c>
+      <c r="N164" s="4" t="inlineStr">
+        <is>
+          <t>666</t>
+        </is>
+      </c>
+      <c r="O164" s="4" t="inlineStr">
+        <is>
+          <t>606</t>
+        </is>
       </c>
     </row>
     <row r="165">
@@ -12065,14 +12904,20 @@
           <t>CAIXABANK, S.A.</t>
         </is>
       </c>
-      <c r="M165" t="n">
-        <v>666</v>
-      </c>
-      <c r="N165" t="n">
-        <v>666</v>
-      </c>
-      <c r="O165" t="n">
-        <v>606</v>
+      <c r="M165" s="4" t="inlineStr">
+        <is>
+          <t>666</t>
+        </is>
+      </c>
+      <c r="N165" s="4" t="inlineStr">
+        <is>
+          <t>666</t>
+        </is>
+      </c>
+      <c r="O165" s="4" t="inlineStr">
+        <is>
+          <t>606</t>
+        </is>
       </c>
     </row>
     <row r="166">
@@ -12136,17 +12981,17 @@
           <t>CAIXABANK, S.A.</t>
         </is>
       </c>
-      <c r="M166" t="inlineStr">
+      <c r="M166" s="4" t="inlineStr">
         <is>
           <t>002</t>
         </is>
       </c>
-      <c r="N166" t="inlineStr">
+      <c r="N166" s="4" t="inlineStr">
         <is>
           <t>002</t>
         </is>
       </c>
-      <c r="O166" t="inlineStr">
+      <c r="O166" s="4" t="inlineStr">
         <is>
           <t>002</t>
         </is>
@@ -12213,17 +13058,17 @@
           <t>CAIXABANK, S.A.</t>
         </is>
       </c>
-      <c r="M167" t="inlineStr">
+      <c r="M167" s="4" t="inlineStr">
         <is>
           <t>002</t>
         </is>
       </c>
-      <c r="N167" t="inlineStr">
+      <c r="N167" s="4" t="inlineStr">
         <is>
           <t>002</t>
         </is>
       </c>
-      <c r="O167" t="inlineStr">
+      <c r="O167" s="4" t="inlineStr">
         <is>
           <t>002</t>
         </is>
@@ -12282,14 +13127,20 @@
           <t>Bilbao</t>
         </is>
       </c>
-      <c r="M168" t="n">
-        <v>111</v>
-      </c>
-      <c r="N168" t="n">
-        <v>111</v>
-      </c>
-      <c r="O168" t="n">
-        <v>101</v>
+      <c r="M168" s="4" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="N168" s="4" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="O168" s="4" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
       </c>
     </row>
     <row r="169">
@@ -12353,14 +13204,20 @@
           <t>CAIXABANK, S.A.</t>
         </is>
       </c>
-      <c r="M169" t="n">
-        <v>0</v>
-      </c>
-      <c r="N169" t="n">
-        <v>822</v>
-      </c>
-      <c r="O169" t="n">
-        <v>822</v>
+      <c r="M169" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N169" s="4" t="inlineStr">
+        <is>
+          <t>822</t>
+        </is>
+      </c>
+      <c r="O169" s="4" t="inlineStr">
+        <is>
+          <t>822</t>
+        </is>
       </c>
     </row>
     <row r="170">
@@ -12424,14 +13281,20 @@
           <t>CAIXABANK, S.A.</t>
         </is>
       </c>
-      <c r="M170" t="n">
-        <v>0</v>
-      </c>
-      <c r="N170" t="n">
-        <v>822</v>
-      </c>
-      <c r="O170" t="n">
-        <v>822</v>
+      <c r="M170" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N170" s="4" t="inlineStr">
+        <is>
+          <t>822</t>
+        </is>
+      </c>
+      <c r="O170" s="4" t="inlineStr">
+        <is>
+          <t>822</t>
+        </is>
       </c>
     </row>
     <row r="171">
@@ -12495,14 +13358,20 @@
           <t>CAIXABANK, S.A.</t>
         </is>
       </c>
-      <c r="M171" t="n">
-        <v>181</v>
-      </c>
-      <c r="N171" t="n">
-        <v>181</v>
-      </c>
-      <c r="O171" t="n">
-        <v>181</v>
+      <c r="M171" s="4" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="N171" s="4" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="O171" s="4" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
       </c>
     </row>
     <row r="172">
@@ -12566,14 +13435,20 @@
           <t>CAIXABANK, S.A.</t>
         </is>
       </c>
-      <c r="M172" t="n">
-        <v>181</v>
-      </c>
-      <c r="N172" t="n">
-        <v>181</v>
-      </c>
-      <c r="O172" t="n">
-        <v>181</v>
+      <c r="M172" s="4" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="N172" s="4" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="O172" s="4" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
       </c>
     </row>
     <row r="173">
@@ -12637,14 +13512,20 @@
           <t>CAIXABANK, S.A.</t>
         </is>
       </c>
-      <c r="M173" t="n">
-        <v>777</v>
-      </c>
-      <c r="N173" t="n">
-        <v>777</v>
-      </c>
-      <c r="O173" t="n">
-        <v>707</v>
+      <c r="M173" s="4" t="inlineStr">
+        <is>
+          <t>777</t>
+        </is>
+      </c>
+      <c r="N173" s="4" t="inlineStr">
+        <is>
+          <t>777</t>
+        </is>
+      </c>
+      <c r="O173" s="4" t="inlineStr">
+        <is>
+          <t>707</t>
+        </is>
       </c>
     </row>
     <row r="174">
@@ -12708,14 +13589,20 @@
           <t>CAIXABANK, S.A.</t>
         </is>
       </c>
-      <c r="M174" t="n">
-        <v>777</v>
-      </c>
-      <c r="N174" t="n">
-        <v>777</v>
-      </c>
-      <c r="O174" t="n">
-        <v>707</v>
+      <c r="M174" s="4" t="inlineStr">
+        <is>
+          <t>777</t>
+        </is>
+      </c>
+      <c r="N174" s="4" t="inlineStr">
+        <is>
+          <t>777</t>
+        </is>
+      </c>
+      <c r="O174" s="4" t="inlineStr">
+        <is>
+          <t>707</t>
+        </is>
       </c>
     </row>
     <row r="175">
@@ -12771,14 +13658,20 @@
           <t>CAIXABANK, S.A.</t>
         </is>
       </c>
-      <c r="M175" t="n">
-        <v>777</v>
-      </c>
-      <c r="N175" t="n">
-        <v>777</v>
-      </c>
-      <c r="O175" t="n">
-        <v>707</v>
+      <c r="M175" s="4" t="inlineStr">
+        <is>
+          <t>777</t>
+        </is>
+      </c>
+      <c r="N175" s="4" t="inlineStr">
+        <is>
+          <t>777</t>
+        </is>
+      </c>
+      <c r="O175" s="4" t="inlineStr">
+        <is>
+          <t>707</t>
+        </is>
       </c>
     </row>
     <row r="176">
@@ -12842,14 +13735,20 @@
           <t>CAIXABANK, S.A.</t>
         </is>
       </c>
-      <c r="M176" t="n">
-        <v>999</v>
-      </c>
-      <c r="N176" t="n">
-        <v>999</v>
-      </c>
-      <c r="O176" t="n">
-        <v>909</v>
+      <c r="M176" s="4" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="N176" s="4" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="O176" s="4" t="inlineStr">
+        <is>
+          <t>909</t>
+        </is>
       </c>
     </row>
     <row r="177">
@@ -12913,14 +13812,20 @@
           <t>CAIXABANK, S.A.</t>
         </is>
       </c>
-      <c r="M177" t="n">
-        <v>999</v>
-      </c>
-      <c r="N177" t="n">
-        <v>999</v>
-      </c>
-      <c r="O177" t="n">
-        <v>909</v>
+      <c r="M177" s="4" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="N177" s="4" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="O177" s="4" t="inlineStr">
+        <is>
+          <t>909</t>
+        </is>
       </c>
     </row>
     <row r="178">
@@ -12976,14 +13881,20 @@
           <t>CAIXABANK, S.A.</t>
         </is>
       </c>
-      <c r="M178" t="n">
-        <v>999</v>
-      </c>
-      <c r="N178" t="n">
-        <v>999</v>
-      </c>
-      <c r="O178" t="n">
-        <v>909</v>
+      <c r="M178" s="4" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="N178" s="4" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="O178" s="4" t="inlineStr">
+        <is>
+          <t>909</t>
+        </is>
       </c>
     </row>
     <row r="179">
@@ -13047,14 +13958,20 @@
           <t>CAIXABANK, S.A.</t>
         </is>
       </c>
-      <c r="M179" t="n">
-        <v>0</v>
-      </c>
-      <c r="N179" t="n">
-        <v>663</v>
-      </c>
-      <c r="O179" t="n">
-        <v>663</v>
+      <c r="M179" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N179" s="4" t="inlineStr">
+        <is>
+          <t>663</t>
+        </is>
+      </c>
+      <c r="O179" s="4" t="inlineStr">
+        <is>
+          <t>663</t>
+        </is>
       </c>
     </row>
     <row r="180">
@@ -13118,14 +14035,20 @@
           <t>CAIXABANK, S.A.</t>
         </is>
       </c>
-      <c r="M180" t="n">
-        <v>0</v>
-      </c>
-      <c r="N180" t="n">
-        <v>663</v>
-      </c>
-      <c r="O180" t="n">
-        <v>663</v>
+      <c r="M180" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N180" s="4" t="inlineStr">
+        <is>
+          <t>663</t>
+        </is>
+      </c>
+      <c r="O180" s="4" t="inlineStr">
+        <is>
+          <t>663</t>
+        </is>
       </c>
     </row>
     <row r="181">
@@ -13189,14 +14112,20 @@
           <t>CAIXABANK, S.A.</t>
         </is>
       </c>
-      <c r="M181" t="n">
-        <v>0</v>
-      </c>
-      <c r="N181" t="n">
-        <v>888</v>
-      </c>
-      <c r="O181" t="n">
-        <v>0</v>
+      <c r="M181" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N181" s="4" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="O181" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="182">
@@ -13260,14 +14189,20 @@
           <t>CAIXABANK, S.A.</t>
         </is>
       </c>
-      <c r="M182" t="n">
-        <v>0</v>
-      </c>
-      <c r="N182" t="n">
-        <v>888</v>
-      </c>
-      <c r="O182" t="n">
-        <v>0</v>
+      <c r="M182" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N182" s="4" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="O182" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="183">
@@ -13331,14 +14266,20 @@
           <t>CAIXABANK, S.A.</t>
         </is>
       </c>
-      <c r="M183" t="n">
-        <v>222</v>
-      </c>
-      <c r="N183" t="n">
-        <v>222</v>
-      </c>
-      <c r="O183" t="n">
-        <v>222</v>
+      <c r="M183" s="4" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="N183" s="4" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="O183" s="4" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
       </c>
     </row>
     <row r="184">
@@ -13402,14 +14343,20 @@
           <t>CAIXABANK, S.A.</t>
         </is>
       </c>
-      <c r="M184" t="n">
-        <v>222</v>
-      </c>
-      <c r="N184" t="n">
-        <v>222</v>
-      </c>
-      <c r="O184" t="n">
-        <v>222</v>
+      <c r="M184" s="4" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="N184" s="4" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="O184" s="4" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
       </c>
     </row>
     <row r="185">
@@ -13473,14 +14420,20 @@
           <t>CAIXABANK, S.A.</t>
         </is>
       </c>
-      <c r="M185" t="n">
-        <v>0</v>
-      </c>
-      <c r="N185" t="n">
-        <v>0</v>
-      </c>
-      <c r="O185" t="n">
-        <v>1</v>
+      <c r="M185" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N185" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O185" s="4" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
       </c>
     </row>
     <row r="186">
@@ -13544,14 +14497,20 @@
           <t>CAIXABANK, S.A.</t>
         </is>
       </c>
-      <c r="M186" t="n">
-        <v>0</v>
-      </c>
-      <c r="N186" t="n">
-        <v>0</v>
-      </c>
-      <c r="O186" t="n">
-        <v>1</v>
+      <c r="M186" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N186" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O186" s="4" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
       </c>
     </row>
     <row r="187">
@@ -13615,14 +14574,20 @@
           <t>CAIXABANK, S.A.</t>
         </is>
       </c>
-      <c r="M187" t="n">
-        <v>0</v>
-      </c>
-      <c r="N187" t="n">
-        <v>0</v>
-      </c>
-      <c r="O187" t="n">
-        <v>1</v>
+      <c r="M187" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N187" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O187" s="4" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
       </c>
     </row>
     <row r="188">
@@ -13686,14 +14651,20 @@
           <t>CAIXABANK, S.A.</t>
         </is>
       </c>
-      <c r="M188" t="n">
-        <v>0</v>
-      </c>
-      <c r="N188" t="n">
-        <v>0</v>
-      </c>
-      <c r="O188" t="n">
-        <v>1</v>
+      <c r="M188" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N188" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O188" s="4" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
       </c>
     </row>
     <row r="189">
@@ -13749,14 +14720,20 @@
           <t>CAIXABANK, S.A.</t>
         </is>
       </c>
-      <c r="M189" t="n">
-        <v>0</v>
-      </c>
-      <c r="N189" t="n">
-        <v>0</v>
-      </c>
-      <c r="O189" t="n">
-        <v>1</v>
+      <c r="M189" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N189" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O189" s="4" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
       </c>
     </row>
     <row r="190">
@@ -13820,15 +14797,17 @@
           <t>CAIXABANK, S.A.</t>
         </is>
       </c>
-      <c r="M190" t="n">
-        <v>0</v>
-      </c>
-      <c r="N190" t="inlineStr">
+      <c r="M190" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N190" s="4" t="inlineStr">
         <is>
           <t>021</t>
         </is>
       </c>
-      <c r="O190" t="inlineStr">
+      <c r="O190" s="4" t="inlineStr">
         <is>
           <t>021</t>
         </is>
@@ -13895,15 +14874,17 @@
           <t>CAIXABANK, S.A.</t>
         </is>
       </c>
-      <c r="M191" t="n">
-        <v>0</v>
-      </c>
-      <c r="N191" t="inlineStr">
+      <c r="M191" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N191" s="4" t="inlineStr">
         <is>
           <t>021</t>
         </is>
       </c>
-      <c r="O191" t="inlineStr">
+      <c r="O191" s="4" t="inlineStr">
         <is>
           <t>021</t>
         </is>
@@ -13962,14 +14943,20 @@
           <t>CAIXABANK, S.A.</t>
         </is>
       </c>
-      <c r="M192" t="n">
-        <v>0</v>
-      </c>
-      <c r="N192" t="n">
-        <v>0</v>
-      </c>
-      <c r="O192" t="n">
-        <v>0</v>
+      <c r="M192" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N192" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O192" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="193">
@@ -14033,15 +15020,17 @@
           <t>CAIXABANK, S.A.</t>
         </is>
       </c>
-      <c r="M193" t="n">
-        <v>0</v>
-      </c>
-      <c r="N193" t="inlineStr">
+      <c r="M193" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N193" s="4" t="inlineStr">
         <is>
           <t>021</t>
         </is>
       </c>
-      <c r="O193" t="inlineStr">
+      <c r="O193" s="4" t="inlineStr">
         <is>
           <t>021</t>
         </is>
@@ -14108,15 +15097,17 @@
           <t>CAIXABANK, S.A.</t>
         </is>
       </c>
-      <c r="M194" t="n">
-        <v>0</v>
-      </c>
-      <c r="N194" t="inlineStr">
+      <c r="M194" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N194" s="4" t="inlineStr">
         <is>
           <t>021</t>
         </is>
       </c>
-      <c r="O194" t="inlineStr">
+      <c r="O194" s="4" t="inlineStr">
         <is>
           <t>021</t>
         </is>
@@ -14183,17 +15174,17 @@
           <t>CAIXABANK, S.A.</t>
         </is>
       </c>
-      <c r="M195" t="inlineStr">
+      <c r="M195" s="4" t="inlineStr">
         <is>
           <t>015</t>
         </is>
       </c>
-      <c r="N195" t="inlineStr">
+      <c r="N195" s="4" t="inlineStr">
         <is>
           <t>015</t>
         </is>
       </c>
-      <c r="O195" t="inlineStr">
+      <c r="O195" s="4" t="inlineStr">
         <is>
           <t>080</t>
         </is>
@@ -14260,17 +15251,17 @@
           <t>CAIXABANK, S.A.</t>
         </is>
       </c>
-      <c r="M196" t="inlineStr">
+      <c r="M196" s="4" t="inlineStr">
         <is>
           <t>015</t>
         </is>
       </c>
-      <c r="N196" t="inlineStr">
+      <c r="N196" s="4" t="inlineStr">
         <is>
           <t>015</t>
         </is>
       </c>
-      <c r="O196" t="inlineStr">
+      <c r="O196" s="4" t="inlineStr">
         <is>
           <t>080</t>
         </is>
@@ -14337,15 +15328,17 @@
           <t>CAIXABANK, S.A.</t>
         </is>
       </c>
-      <c r="M197" t="n">
-        <v>0</v>
-      </c>
-      <c r="N197" t="inlineStr">
+      <c r="M197" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N197" s="4" t="inlineStr">
         <is>
           <t>020</t>
         </is>
       </c>
-      <c r="O197" t="inlineStr">
+      <c r="O197" s="4" t="inlineStr">
         <is>
           <t>020</t>
         </is>
@@ -14412,15 +15405,17 @@
           <t>CAIXABANK, S.A.</t>
         </is>
       </c>
-      <c r="M198" t="n">
-        <v>0</v>
-      </c>
-      <c r="N198" t="inlineStr">
+      <c r="M198" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N198" s="4" t="inlineStr">
         <is>
           <t>020</t>
         </is>
       </c>
-      <c r="O198" t="inlineStr">
+      <c r="O198" s="4" t="inlineStr">
         <is>
           <t>020</t>
         </is>
@@ -14487,14 +15482,20 @@
           <t>CAIXABANK, S.A.</t>
         </is>
       </c>
-      <c r="M199" t="n">
-        <v>222</v>
-      </c>
-      <c r="N199" t="n">
-        <v>222</v>
-      </c>
-      <c r="O199" t="n">
-        <v>202</v>
+      <c r="M199" s="4" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="N199" s="4" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="O199" s="4" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
       </c>
     </row>
     <row r="200">
@@ -14558,14 +15559,20 @@
           <t>CAIXABANK, S.A.</t>
         </is>
       </c>
-      <c r="M200" t="n">
-        <v>222</v>
-      </c>
-      <c r="N200" t="n">
-        <v>222</v>
-      </c>
-      <c r="O200" t="n">
-        <v>202</v>
+      <c r="M200" s="4" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="N200" s="4" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="O200" s="4" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
       </c>
     </row>
     <row r="201">
@@ -14629,14 +15636,20 @@
           <t>Alicante Pagos</t>
         </is>
       </c>
-      <c r="M201" t="n">
-        <v>666</v>
-      </c>
-      <c r="N201" t="n">
-        <v>666</v>
-      </c>
-      <c r="O201" t="n">
-        <v>606</v>
+      <c r="M201" s="4" t="inlineStr">
+        <is>
+          <t>666</t>
+        </is>
+      </c>
+      <c r="N201" s="4" t="inlineStr">
+        <is>
+          <t>666</t>
+        </is>
+      </c>
+      <c r="O201" s="4" t="inlineStr">
+        <is>
+          <t>606</t>
+        </is>
       </c>
     </row>
     <row r="202">
@@ -14700,14 +15713,20 @@
           <t>Alicante Cobros</t>
         </is>
       </c>
-      <c r="M202" t="n">
-        <v>666</v>
-      </c>
-      <c r="N202" t="n">
-        <v>666</v>
-      </c>
-      <c r="O202" t="n">
-        <v>606</v>
+      <c r="M202" s="4" t="inlineStr">
+        <is>
+          <t>666</t>
+        </is>
+      </c>
+      <c r="N202" s="4" t="inlineStr">
+        <is>
+          <t>666</t>
+        </is>
+      </c>
+      <c r="O202" s="4" t="inlineStr">
+        <is>
+          <t>606</t>
+        </is>
       </c>
     </row>
     <row r="203">
@@ -14771,14 +15790,20 @@
           <t>Bilbao Pagos</t>
         </is>
       </c>
-      <c r="M203" t="n">
-        <v>666</v>
-      </c>
-      <c r="N203" t="n">
-        <v>666</v>
-      </c>
-      <c r="O203" t="n">
-        <v>606</v>
+      <c r="M203" s="4" t="inlineStr">
+        <is>
+          <t>666</t>
+        </is>
+      </c>
+      <c r="N203" s="4" t="inlineStr">
+        <is>
+          <t>666</t>
+        </is>
+      </c>
+      <c r="O203" s="4" t="inlineStr">
+        <is>
+          <t>606</t>
+        </is>
       </c>
     </row>
     <row r="204">
@@ -14842,14 +15867,20 @@
           <t>Bilbao Cobros</t>
         </is>
       </c>
-      <c r="M204" t="n">
-        <v>666</v>
-      </c>
-      <c r="N204" t="n">
-        <v>666</v>
-      </c>
-      <c r="O204" t="n">
-        <v>606</v>
+      <c r="M204" s="4" t="inlineStr">
+        <is>
+          <t>666</t>
+        </is>
+      </c>
+      <c r="N204" s="4" t="inlineStr">
+        <is>
+          <t>666</t>
+        </is>
+      </c>
+      <c r="O204" s="4" t="inlineStr">
+        <is>
+          <t>606</t>
+        </is>
       </c>
     </row>
     <row r="205">
@@ -14913,14 +15944,20 @@
           <t>Girona Pagos</t>
         </is>
       </c>
-      <c r="M205" t="n">
-        <v>777</v>
-      </c>
-      <c r="N205" t="n">
-        <v>777</v>
-      </c>
-      <c r="O205" t="n">
-        <v>707</v>
+      <c r="M205" s="4" t="inlineStr">
+        <is>
+          <t>777</t>
+        </is>
+      </c>
+      <c r="N205" s="4" t="inlineStr">
+        <is>
+          <t>777</t>
+        </is>
+      </c>
+      <c r="O205" s="4" t="inlineStr">
+        <is>
+          <t>707</t>
+        </is>
       </c>
     </row>
     <row r="206">
@@ -14984,14 +16021,20 @@
           <t>Girona Cobros</t>
         </is>
       </c>
-      <c r="M206" t="n">
-        <v>777</v>
-      </c>
-      <c r="N206" t="n">
-        <v>777</v>
-      </c>
-      <c r="O206" t="n">
-        <v>707</v>
+      <c r="M206" s="4" t="inlineStr">
+        <is>
+          <t>777</t>
+        </is>
+      </c>
+      <c r="N206" s="4" t="inlineStr">
+        <is>
+          <t>777</t>
+        </is>
+      </c>
+      <c r="O206" s="4" t="inlineStr">
+        <is>
+          <t>707</t>
+        </is>
       </c>
     </row>
     <row r="207">
@@ -15055,14 +16098,20 @@
           <t>BANCO DE SABADELL, S.A.</t>
         </is>
       </c>
-      <c r="M207" t="n">
-        <v>999</v>
-      </c>
-      <c r="N207" t="n">
-        <v>999</v>
-      </c>
-      <c r="O207" t="n">
-        <v>909</v>
+      <c r="M207" s="4" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="N207" s="4" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="O207" s="4" t="inlineStr">
+        <is>
+          <t>909</t>
+        </is>
       </c>
     </row>
     <row r="208">
@@ -15126,14 +16175,20 @@
           <t>BANCO DE SABADELL, S.A.</t>
         </is>
       </c>
-      <c r="M208" t="n">
-        <v>999</v>
-      </c>
-      <c r="N208" t="n">
-        <v>999</v>
-      </c>
-      <c r="O208" t="n">
-        <v>909</v>
+      <c r="M208" s="4" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="N208" s="4" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="O208" s="4" t="inlineStr">
+        <is>
+          <t>909</t>
+        </is>
       </c>
     </row>
     <row r="209">
@@ -15197,14 +16252,20 @@
           <t>Menorca Pagos</t>
         </is>
       </c>
-      <c r="M209" t="n">
-        <v>555</v>
-      </c>
-      <c r="N209" t="n">
-        <v>555</v>
-      </c>
-      <c r="O209" t="n">
-        <v>505</v>
+      <c r="M209" s="4" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="N209" s="4" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="O209" s="4" t="inlineStr">
+        <is>
+          <t>505</t>
+        </is>
       </c>
     </row>
     <row r="210">
@@ -15268,14 +16329,20 @@
           <t>Menorca Cobros</t>
         </is>
       </c>
-      <c r="M210" t="n">
-        <v>555</v>
-      </c>
-      <c r="N210" t="n">
-        <v>555</v>
-      </c>
-      <c r="O210" t="n">
-        <v>505</v>
+      <c r="M210" s="4" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="N210" s="4" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="O210" s="4" t="inlineStr">
+        <is>
+          <t>505</t>
+        </is>
       </c>
     </row>
     <row r="211">
@@ -15339,14 +16406,20 @@
           <t>Palma de Mallorca Pagos</t>
         </is>
       </c>
-      <c r="M211" t="n">
-        <v>333</v>
-      </c>
-      <c r="N211" t="n">
-        <v>333</v>
-      </c>
-      <c r="O211" t="n">
-        <v>303</v>
+      <c r="M211" s="4" t="inlineStr">
+        <is>
+          <t>333</t>
+        </is>
+      </c>
+      <c r="N211" s="4" t="inlineStr">
+        <is>
+          <t>333</t>
+        </is>
+      </c>
+      <c r="O211" s="4" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
       </c>
     </row>
     <row r="212">
@@ -15410,14 +16483,20 @@
           <t>Palma de Mallorca Cobros</t>
         </is>
       </c>
-      <c r="M212" t="n">
-        <v>333</v>
-      </c>
-      <c r="N212" t="n">
-        <v>333</v>
-      </c>
-      <c r="O212" t="n">
-        <v>303</v>
+      <c r="M212" s="4" t="inlineStr">
+        <is>
+          <t>333</t>
+        </is>
+      </c>
+      <c r="N212" s="4" t="inlineStr">
+        <is>
+          <t>333</t>
+        </is>
+      </c>
+      <c r="O212" s="4" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
       </c>
     </row>
     <row r="213">
@@ -15481,14 +16560,20 @@
           <t>Son Bonet Pagos</t>
         </is>
       </c>
-      <c r="M213" t="n">
-        <v>444</v>
-      </c>
-      <c r="N213" t="n">
-        <v>444</v>
-      </c>
-      <c r="O213" t="n">
-        <v>404</v>
+      <c r="M213" s="4" t="inlineStr">
+        <is>
+          <t>444</t>
+        </is>
+      </c>
+      <c r="N213" s="4" t="inlineStr">
+        <is>
+          <t>444</t>
+        </is>
+      </c>
+      <c r="O213" s="4" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
       </c>
     </row>
     <row r="214">
@@ -15552,14 +16637,20 @@
           <t>Son Bonet Cobros</t>
         </is>
       </c>
-      <c r="M214" t="n">
-        <v>444</v>
-      </c>
-      <c r="N214" t="n">
-        <v>444</v>
-      </c>
-      <c r="O214" t="n">
-        <v>404</v>
+      <c r="M214" s="4" t="inlineStr">
+        <is>
+          <t>444</t>
+        </is>
+      </c>
+      <c r="N214" s="4" t="inlineStr">
+        <is>
+          <t>444</t>
+        </is>
+      </c>
+      <c r="O214" s="4" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
       </c>
     </row>
     <row r="215">
@@ -15623,14 +16714,20 @@
           <t>Tenerife Norte Pagos</t>
         </is>
       </c>
-      <c r="M215" t="n">
-        <v>888</v>
-      </c>
-      <c r="N215" t="n">
-        <v>888</v>
-      </c>
-      <c r="O215" t="n">
-        <v>808</v>
+      <c r="M215" s="4" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="N215" s="4" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="O215" s="4" t="inlineStr">
+        <is>
+          <t>808</t>
+        </is>
       </c>
     </row>
     <row r="216">
@@ -15694,14 +16791,20 @@
           <t>BANCO DE SABADELL, S.A.</t>
         </is>
       </c>
-      <c r="M216" t="n">
-        <v>888</v>
-      </c>
-      <c r="N216" t="n">
-        <v>888</v>
-      </c>
-      <c r="O216" t="n">
-        <v>808</v>
+      <c r="M216" s="4" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="N216" s="4" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="O216" s="4" t="inlineStr">
+        <is>
+          <t>808</t>
+        </is>
       </c>
     </row>
     <row r="217">
@@ -15765,14 +16868,20 @@
           <t>Valencia Pagos</t>
         </is>
       </c>
-      <c r="M217" t="n">
-        <v>222</v>
-      </c>
-      <c r="N217" t="n">
-        <v>222</v>
-      </c>
-      <c r="O217" t="n">
-        <v>202</v>
+      <c r="M217" s="4" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="N217" s="4" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="O217" s="4" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
       </c>
     </row>
     <row r="218">
@@ -15836,14 +16945,20 @@
           <t>Valencia Cobros</t>
         </is>
       </c>
-      <c r="M218" t="n">
-        <v>222</v>
-      </c>
-      <c r="N218" t="n">
-        <v>222</v>
-      </c>
-      <c r="O218" t="n">
-        <v>202</v>
+      <c r="M218" s="4" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="N218" s="4" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="O218" s="4" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
       </c>
     </row>
     <row r="219">
@@ -15907,14 +17022,20 @@
           <t>UNICAJA BANCO, S.A.</t>
         </is>
       </c>
-      <c r="M219" t="n">
-        <v>0</v>
-      </c>
-      <c r="N219" t="n">
-        <v>0</v>
-      </c>
-      <c r="O219" t="n">
-        <v>0</v>
+      <c r="M219" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N219" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O219" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="220">
@@ -15978,14 +17099,20 @@
           <t>UNICAJA BANCO, S.A.</t>
         </is>
       </c>
-      <c r="M220" t="n">
-        <v>0</v>
-      </c>
-      <c r="N220" t="n">
-        <v>0</v>
-      </c>
-      <c r="O220" t="n">
-        <v>0</v>
+      <c r="M220" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N220" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O220" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="221">
@@ -16041,18 +17168,20 @@
           <t>UNICAJA BANCO, S.A.</t>
         </is>
       </c>
-      <c r="M221" t="inlineStr">
+      <c r="M221" s="4" t="inlineStr">
         <is>
           <t>003</t>
         </is>
       </c>
-      <c r="N221" t="inlineStr">
+      <c r="N221" s="4" t="inlineStr">
         <is>
           <t>003</t>
         </is>
       </c>
-      <c r="O221" t="n">
-        <v>0</v>
+      <c r="O221" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="222">
@@ -16108,18 +17237,20 @@
           <t>UNICAJA BANCO, S.A.</t>
         </is>
       </c>
-      <c r="M222" t="inlineStr">
+      <c r="M222" s="4" t="inlineStr">
         <is>
           <t>003</t>
         </is>
       </c>
-      <c r="N222" t="inlineStr">
+      <c r="N222" s="4" t="inlineStr">
         <is>
           <t>003</t>
         </is>
       </c>
-      <c r="O222" t="n">
-        <v>0</v>
+      <c r="O222" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="223">
@@ -16175,14 +17306,20 @@
           <t>UNICAJA BANCO, S.A.</t>
         </is>
       </c>
-      <c r="M223" t="n">
-        <v>0</v>
-      </c>
-      <c r="N223" t="n">
-        <v>0</v>
-      </c>
-      <c r="O223" t="n">
-        <v>0</v>
+      <c r="M223" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N223" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O223" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="224">
@@ -16238,14 +17375,20 @@
           <t>UNICAJA BANCO, S.A.</t>
         </is>
       </c>
-      <c r="M224" t="n">
-        <v>0</v>
-      </c>
-      <c r="N224" t="n">
-        <v>0</v>
-      </c>
-      <c r="O224" t="n">
-        <v>0</v>
+      <c r="M224" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N224" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O224" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="225">
@@ -16309,17 +17452,17 @@
           <t>UNICAJA BANCO, S.A.</t>
         </is>
       </c>
-      <c r="M225" t="inlineStr">
+      <c r="M225" s="4" t="inlineStr">
         <is>
           <t>007</t>
         </is>
       </c>
-      <c r="N225" t="inlineStr">
+      <c r="N225" s="4" t="inlineStr">
         <is>
           <t>007</t>
         </is>
       </c>
-      <c r="O225" t="inlineStr">
+      <c r="O225" s="4" t="inlineStr">
         <is>
           <t>007</t>
         </is>
@@ -16386,17 +17529,17 @@
           <t>UNICAJA BANCO, S.A.</t>
         </is>
       </c>
-      <c r="M226" t="inlineStr">
+      <c r="M226" s="4" t="inlineStr">
         <is>
           <t>007</t>
         </is>
       </c>
-      <c r="N226" t="inlineStr">
+      <c r="N226" s="4" t="inlineStr">
         <is>
           <t>007</t>
         </is>
       </c>
-      <c r="O226" t="inlineStr">
+      <c r="O226" s="4" t="inlineStr">
         <is>
           <t>007</t>
         </is>
@@ -16463,17 +17606,17 @@
           <t>UNICAJA BANCO, S.A.</t>
         </is>
       </c>
-      <c r="M227" t="inlineStr">
+      <c r="M227" s="4" t="inlineStr">
         <is>
           <t>005</t>
         </is>
       </c>
-      <c r="N227" t="inlineStr">
+      <c r="N227" s="4" t="inlineStr">
         <is>
           <t>005</t>
         </is>
       </c>
-      <c r="O227" t="inlineStr">
+      <c r="O227" s="4" t="inlineStr">
         <is>
           <t>005</t>
         </is>
@@ -16540,17 +17683,17 @@
           <t>UNICAJA BANCO, S.A.</t>
         </is>
       </c>
-      <c r="M228" t="inlineStr">
+      <c r="M228" s="4" t="inlineStr">
         <is>
           <t>005</t>
         </is>
       </c>
-      <c r="N228" t="inlineStr">
+      <c r="N228" s="4" t="inlineStr">
         <is>
           <t>005</t>
         </is>
       </c>
-      <c r="O228" t="inlineStr">
+      <c r="O228" s="4" t="inlineStr">
         <is>
           <t>005</t>
         </is>
@@ -16617,17 +17760,17 @@
           <t>UNICAJA BANCO, S.A.</t>
         </is>
       </c>
-      <c r="M229" t="inlineStr">
+      <c r="M229" s="4" t="inlineStr">
         <is>
           <t>001</t>
         </is>
       </c>
-      <c r="N229" t="inlineStr">
+      <c r="N229" s="4" t="inlineStr">
         <is>
           <t>001</t>
         </is>
       </c>
-      <c r="O229" t="inlineStr">
+      <c r="O229" s="4" t="inlineStr">
         <is>
           <t>001</t>
         </is>
@@ -16694,17 +17837,17 @@
           <t>UNICAJA BANCO, S.A.</t>
         </is>
       </c>
-      <c r="M230" t="inlineStr">
+      <c r="M230" s="4" t="inlineStr">
         <is>
           <t>001</t>
         </is>
       </c>
-      <c r="N230" t="inlineStr">
+      <c r="N230" s="4" t="inlineStr">
         <is>
           <t>001</t>
         </is>
       </c>
-      <c r="O230" t="inlineStr">
+      <c r="O230" s="4" t="inlineStr">
         <is>
           <t>001</t>
         </is>
@@ -16771,18 +17914,20 @@
           <t>UNICAJA BANCO, S.A.</t>
         </is>
       </c>
-      <c r="M231" t="inlineStr">
+      <c r="M231" s="4" t="inlineStr">
         <is>
           <t>006</t>
         </is>
       </c>
-      <c r="N231" t="inlineStr">
+      <c r="N231" s="4" t="inlineStr">
         <is>
           <t>006</t>
         </is>
       </c>
-      <c r="O231" t="n">
-        <v>0</v>
+      <c r="O231" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="232">
@@ -16846,18 +17991,20 @@
           <t>UNICAJA BANCO, S.A.</t>
         </is>
       </c>
-      <c r="M232" t="inlineStr">
+      <c r="M232" s="4" t="inlineStr">
         <is>
           <t>006</t>
         </is>
       </c>
-      <c r="N232" t="inlineStr">
+      <c r="N232" s="4" t="inlineStr">
         <is>
           <t>006</t>
         </is>
       </c>
-      <c r="O232" t="n">
-        <v>0</v>
+      <c r="O232" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="233">
@@ -16921,18 +18068,20 @@
           <t>UNICAJA BANCO, S.A.</t>
         </is>
       </c>
-      <c r="M233" t="inlineStr">
+      <c r="M233" s="4" t="inlineStr">
         <is>
           <t>006</t>
         </is>
       </c>
-      <c r="N233" t="inlineStr">
+      <c r="N233" s="4" t="inlineStr">
         <is>
           <t>006</t>
         </is>
       </c>
-      <c r="O233" t="n">
-        <v>0</v>
+      <c r="O233" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="234">
@@ -16996,18 +18145,20 @@
           <t>UNICAJA BANCO, S.A.</t>
         </is>
       </c>
-      <c r="M234" t="inlineStr">
+      <c r="M234" s="4" t="inlineStr">
         <is>
           <t>006</t>
         </is>
       </c>
-      <c r="N234" t="inlineStr">
+      <c r="N234" s="4" t="inlineStr">
         <is>
           <t>006</t>
         </is>
       </c>
-      <c r="O234" t="n">
-        <v>0</v>
+      <c r="O234" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="235">
@@ -17071,18 +18222,20 @@
           <t>UNICAJA BANCO, S.A.</t>
         </is>
       </c>
-      <c r="M235" t="inlineStr">
+      <c r="M235" s="4" t="inlineStr">
         <is>
           <t>006</t>
         </is>
       </c>
-      <c r="N235" t="inlineStr">
+      <c r="N235" s="4" t="inlineStr">
         <is>
           <t>006</t>
         </is>
       </c>
-      <c r="O235" t="n">
-        <v>0</v>
+      <c r="O235" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="236">
@@ -17146,18 +18299,20 @@
           <t>UNICAJA BANCO, S.A.</t>
         </is>
       </c>
-      <c r="M236" t="inlineStr">
+      <c r="M236" s="4" t="inlineStr">
         <is>
           <t>006</t>
         </is>
       </c>
-      <c r="N236" t="inlineStr">
+      <c r="N236" s="4" t="inlineStr">
         <is>
           <t>006</t>
         </is>
       </c>
-      <c r="O236" t="n">
-        <v>0</v>
+      <c r="O236" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="237">
@@ -17221,17 +18376,17 @@
           <t>UNICAJA BANCO, S.A.</t>
         </is>
       </c>
-      <c r="M237" t="inlineStr">
+      <c r="M237" s="4" t="inlineStr">
         <is>
           <t>008</t>
         </is>
       </c>
-      <c r="N237" t="inlineStr">
+      <c r="N237" s="4" t="inlineStr">
         <is>
           <t>008</t>
         </is>
       </c>
-      <c r="O237" t="inlineStr">
+      <c r="O237" s="4" t="inlineStr">
         <is>
           <t>008</t>
         </is>
@@ -17298,17 +18453,17 @@
           <t>UNICAJA BANCO, S.A.</t>
         </is>
       </c>
-      <c r="M238" t="inlineStr">
+      <c r="M238" s="4" t="inlineStr">
         <is>
           <t>008</t>
         </is>
       </c>
-      <c r="N238" t="inlineStr">
+      <c r="N238" s="4" t="inlineStr">
         <is>
           <t>008</t>
         </is>
       </c>
-      <c r="O238" t="inlineStr">
+      <c r="O238" s="4" t="inlineStr">
         <is>
           <t>008</t>
         </is>
@@ -17375,17 +18530,17 @@
           <t>UNICAJA BANCO, S.A.</t>
         </is>
       </c>
-      <c r="M239" t="inlineStr">
+      <c r="M239" s="4" t="inlineStr">
         <is>
           <t>002</t>
         </is>
       </c>
-      <c r="N239" t="inlineStr">
+      <c r="N239" s="4" t="inlineStr">
         <is>
           <t>002</t>
         </is>
       </c>
-      <c r="O239" t="inlineStr">
+      <c r="O239" s="4" t="inlineStr">
         <is>
           <t>002</t>
         </is>
@@ -17452,17 +18607,17 @@
           <t>UNICAJA BANCO, S.A.</t>
         </is>
       </c>
-      <c r="M240" t="inlineStr">
+      <c r="M240" s="4" t="inlineStr">
         <is>
           <t>002</t>
         </is>
       </c>
-      <c r="N240" t="inlineStr">
+      <c r="N240" s="4" t="inlineStr">
         <is>
           <t>002</t>
         </is>
       </c>
-      <c r="O240" t="inlineStr">
+      <c r="O240" s="4" t="inlineStr">
         <is>
           <t>002</t>
         </is>
@@ -17529,14 +18684,20 @@
           <t>BANCO BILBAO VIZCAYA ARGENTARIA, S.A.</t>
         </is>
       </c>
-      <c r="M241" t="n">
-        <v>0</v>
-      </c>
-      <c r="N241" t="n">
-        <v>0</v>
-      </c>
-      <c r="O241" t="n">
-        <v>0</v>
+      <c r="M241" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N241" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O241" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="242">
@@ -17600,14 +18761,20 @@
           <t>BANCO BILBAO VIZCAYA ARGENTARIA, S.A.</t>
         </is>
       </c>
-      <c r="M242" t="n">
-        <v>0</v>
-      </c>
-      <c r="N242" t="n">
-        <v>0</v>
-      </c>
-      <c r="O242" t="n">
-        <v>0</v>
+      <c r="M242" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N242" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O242" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="243">
@@ -17671,15 +18838,17 @@
           <t>ADIN BKT EUROS GRAL COBROS Y PAGOS</t>
         </is>
       </c>
-      <c r="M243" t="n">
-        <v>0</v>
-      </c>
-      <c r="N243" t="inlineStr">
+      <c r="M243" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N243" s="4" t="inlineStr">
         <is>
           <t>023</t>
         </is>
       </c>
-      <c r="O243" t="inlineStr">
+      <c r="O243" s="4" t="inlineStr">
         <is>
           <t>023</t>
         </is>
@@ -17746,15 +18915,17 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M244" t="n">
-        <v>0</v>
-      </c>
-      <c r="N244" t="inlineStr">
+      <c r="M244" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N244" s="4" t="inlineStr">
         <is>
           <t>023</t>
         </is>
       </c>
-      <c r="O244" t="inlineStr">
+      <c r="O244" s="4" t="inlineStr">
         <is>
           <t>023</t>
         </is>
@@ -17821,15 +18992,17 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M245" t="n">
-        <v>0</v>
-      </c>
-      <c r="N245" t="inlineStr">
+      <c r="M245" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N245" s="4" t="inlineStr">
         <is>
           <t>023</t>
         </is>
       </c>
-      <c r="O245" t="inlineStr">
+      <c r="O245" s="4" t="inlineStr">
         <is>
           <t>023</t>
         </is>
@@ -17896,15 +19069,17 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M246" t="n">
-        <v>0</v>
-      </c>
-      <c r="N246" t="inlineStr">
+      <c r="M246" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N246" s="4" t="inlineStr">
         <is>
           <t>023</t>
         </is>
       </c>
-      <c r="O246" t="inlineStr">
+      <c r="O246" s="4" t="inlineStr">
         <is>
           <t>023</t>
         </is>
@@ -17971,15 +19146,17 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M247" t="n">
-        <v>0</v>
-      </c>
-      <c r="N247" t="inlineStr">
+      <c r="M247" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N247" s="4" t="inlineStr">
         <is>
           <t>023</t>
         </is>
       </c>
-      <c r="O247" t="inlineStr">
+      <c r="O247" s="4" t="inlineStr">
         <is>
           <t>023</t>
         </is>
@@ -18046,15 +19223,17 @@
           <t>BANKINTER, S.A.</t>
         </is>
       </c>
-      <c r="M248" t="n">
-        <v>0</v>
-      </c>
-      <c r="N248" t="inlineStr">
+      <c r="M248" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N248" s="4" t="inlineStr">
         <is>
           <t>023</t>
         </is>
       </c>
-      <c r="O248" t="inlineStr">
+      <c r="O248" s="4" t="inlineStr">
         <is>
           <t>023</t>
         </is>
@@ -18121,14 +19300,20 @@
           <t>BANCO SANTANDER, S.A.</t>
         </is>
       </c>
-      <c r="M249" t="n">
-        <v>0</v>
-      </c>
-      <c r="N249" t="n">
-        <v>282</v>
-      </c>
-      <c r="O249" t="n">
-        <v>0</v>
+      <c r="M249" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N249" s="4" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="O249" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="250">
@@ -18192,14 +19377,20 @@
           <t>BANCO SANTANDER, S.A.</t>
         </is>
       </c>
-      <c r="M250" t="n">
-        <v>0</v>
-      </c>
-      <c r="N250" t="n">
-        <v>282</v>
-      </c>
-      <c r="O250" t="n">
-        <v>0</v>
+      <c r="M250" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N250" s="4" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="O250" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
       </c>
     </row>
     <row r="251">
@@ -18263,17 +19454,17 @@
           <t>CAIXABANK, S.A.</t>
         </is>
       </c>
-      <c r="M251" t="inlineStr">
+      <c r="M251" s="4" t="inlineStr">
         <is>
           <t>002</t>
         </is>
       </c>
-      <c r="N251" t="inlineStr">
+      <c r="N251" s="4" t="inlineStr">
         <is>
           <t>002</t>
         </is>
       </c>
-      <c r="O251" t="inlineStr">
+      <c r="O251" s="4" t="inlineStr">
         <is>
           <t>002</t>
         </is>
@@ -18340,17 +19531,17 @@
           <t>CAIXABANK, S.A.</t>
         </is>
       </c>
-      <c r="M252" t="inlineStr">
+      <c r="M252" s="4" t="inlineStr">
         <is>
           <t>002</t>
         </is>
       </c>
-      <c r="N252" t="inlineStr">
+      <c r="N252" s="4" t="inlineStr">
         <is>
           <t>002</t>
         </is>
       </c>
-      <c r="O252" t="inlineStr">
+      <c r="O252" s="4" t="inlineStr">
         <is>
           <t>002</t>
         </is>
@@ -18415,6 +19606,9 @@
           <t>CAIXABANK, S.A.</t>
         </is>
       </c>
+      <c r="M253" s="4" t="n"/>
+      <c r="N253" s="4" t="n"/>
+      <c r="O253" s="4" t="n"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -18477,17 +19671,17 @@
           <t>CAIXABANK, S.A.</t>
         </is>
       </c>
-      <c r="M254" t="inlineStr">
+      <c r="M254" s="4" t="inlineStr">
         <is>
           <t>002</t>
         </is>
       </c>
-      <c r="N254" t="inlineStr">
+      <c r="N254" s="4" t="inlineStr">
         <is>
           <t>002</t>
         </is>
       </c>
-      <c r="O254" t="inlineStr">
+      <c r="O254" s="4" t="inlineStr">
         <is>
           <t>002</t>
         </is>
@@ -18554,14 +19748,20 @@
           <t>CAIXABANK, S.A.</t>
         </is>
       </c>
-      <c r="M255" t="n">
-        <v>0</v>
-      </c>
-      <c r="N255" t="n">
-        <v>0</v>
-      </c>
-      <c r="O255" t="n">
-        <v>1</v>
+      <c r="M255" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N255" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O255" s="4" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
       </c>
     </row>
     <row r="256">
@@ -18625,14 +19825,20 @@
           <t>Banco Pagos Concesión AIRM</t>
         </is>
       </c>
-      <c r="M256" t="n">
-        <v>0</v>
-      </c>
-      <c r="N256" t="n">
-        <v>0</v>
-      </c>
-      <c r="O256" t="n">
-        <v>1</v>
+      <c r="M256" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N256" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O256" s="4" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
       </c>
     </row>
     <row r="257">
@@ -18696,14 +19902,20 @@
           <t>Banco Cobros Concesión AIRM</t>
         </is>
       </c>
-      <c r="M257" t="n">
-        <v>0</v>
-      </c>
-      <c r="N257" t="n">
-        <v>0</v>
-      </c>
-      <c r="O257" t="n">
-        <v>1</v>
+      <c r="M257" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N257" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O257" s="4" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
       </c>
     </row>
     <row r="258">
@@ -18767,14 +19979,20 @@
           <t>CAIXABANK, S.A.</t>
         </is>
       </c>
-      <c r="M258" t="n">
-        <v>0</v>
-      </c>
-      <c r="N258" t="n">
-        <v>0</v>
-      </c>
-      <c r="O258" t="n">
-        <v>1</v>
+      <c r="M258" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N258" s="4" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="O258" s="4" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
       </c>
     </row>
   </sheetData>
